--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16040"/>
+    <workbookView windowHeight="16080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -454,6 +454,66 @@
   </si>
   <si>
     <t>主动退出</t>
+  </si>
+  <si>
+    <t>UIFormType</t>
+  </si>
+  <si>
+    <t>界面类型</t>
+  </si>
+  <si>
+    <t>Undefined</t>
+  </si>
+  <si>
+    <t>未定义</t>
+  </si>
+  <si>
+    <t>DialogForm</t>
+  </si>
+  <si>
+    <t>弹出框</t>
+  </si>
+  <si>
+    <t>LobbyForm</t>
+  </si>
+  <si>
+    <t>大厅界面</t>
+  </si>
+  <si>
+    <t>SettingForm</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>AboutForm</t>
+  </si>
+  <si>
+    <t>关于</t>
+  </si>
+  <si>
+    <t>SceneType</t>
+  </si>
+  <si>
+    <t>场景类型</t>
+  </si>
+  <si>
+    <t>Launch</t>
+  </si>
+  <si>
+    <t>启动场景</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>菜单场景</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>主场景</t>
   </si>
 </sst>
 </file>
@@ -508,34 +568,33 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -543,15 +602,13 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -559,7 +616,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -567,7 +623,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -575,91 +630,73 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -704,18 +741,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -728,19 +753,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,19 +777,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,19 +801,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,19 +825,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -824,19 +849,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,19 +873,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -947,7 +972,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1018,82 +1043,88 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1102,10 +1133,10 @@
     <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1114,10 +1145,10 @@
     <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1126,10 +1157,10 @@
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1138,10 +1169,10 @@
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1150,24 +1181,18 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1185,6 +1210,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1656,7 +1683,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -2935,6 +2962,190 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
+    <row r="60" customHeight="1" spans="1:12">
+      <c r="A60" s="7"/>
+      <c r="B60" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J60" s="7">
+        <v>0</v>
+      </c>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:12">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="J61" s="7">
+        <v>1</v>
+      </c>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="J62" s="7">
+        <v>100</v>
+      </c>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:12">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J63" s="7">
+        <v>101</v>
+      </c>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:12">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J64" s="7">
+        <v>102</v>
+      </c>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:12">
+      <c r="A66" s="7"/>
+      <c r="B66" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C66" s="7">
+        <v>0</v>
+      </c>
+      <c r="D66" s="7">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J66" s="7">
+        <v>0</v>
+      </c>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:12">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J67" s="7">
+        <v>1</v>
+      </c>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:12">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="J68" s="7">
+        <v>2</v>
+      </c>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowHeight="16660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="158">
   <si>
     <t>##var</t>
   </si>
@@ -434,84 +434,6 @@
     <t>主场景</t>
   </si>
   <si>
-    <t>BattleActionType</t>
-  </si>
-  <si>
-    <t>战斗行动类型</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>道具</t>
-  </si>
-  <si>
-    <t>Escape</t>
-  </si>
-  <si>
-    <t>逃跑</t>
-  </si>
-  <si>
-    <t>BattleTargetType</t>
-  </si>
-  <si>
-    <t>战斗目标类型</t>
-  </si>
-  <si>
-    <t>Self</t>
-  </si>
-  <si>
-    <t>自己</t>
-  </si>
-  <si>
-    <t>SingleAlly</t>
-  </si>
-  <si>
-    <t>单个友方</t>
-  </si>
-  <si>
-    <t>AllAllies</t>
-  </si>
-  <si>
-    <t>全体友方</t>
-  </si>
-  <si>
-    <t>SingleEnemy</t>
-  </si>
-  <si>
-    <t>单个敌方</t>
-  </si>
-  <si>
-    <t>AllEnemies</t>
-  </si>
-  <si>
-    <t>全体敌方</t>
-  </si>
-  <si>
-    <t>BattleStatusType</t>
-  </si>
-  <si>
-    <t>战斗状态类型</t>
-  </si>
-  <si>
-    <t>Stun</t>
-  </si>
-  <si>
-    <t>眩晕</t>
-  </si>
-  <si>
     <r>
       <t>全名</t>
     </r>
@@ -544,6 +466,144 @@
     </r>
   </si>
   <si>
+    <t>BattleActionType</t>
+  </si>
+  <si>
+    <t>战斗行动类型</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>Escape</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>BattleTargetType</t>
+  </si>
+  <si>
+    <t>战斗目标类型</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>自己</t>
+  </si>
+  <si>
+    <t>SingleAlly</t>
+  </si>
+  <si>
+    <t>单个友方</t>
+  </si>
+  <si>
+    <t>AllAllies</t>
+  </si>
+  <si>
+    <t>全体友方</t>
+  </si>
+  <si>
+    <t>SingleEnemy</t>
+  </si>
+  <si>
+    <t>单个敌方</t>
+  </si>
+  <si>
+    <t>AllEnemies</t>
+  </si>
+  <si>
+    <t>全体敌方</t>
+  </si>
+  <si>
+    <t>BattleStateType</t>
+  </si>
+  <si>
+    <t>战斗状态类型</t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>BattleOutcomeType</t>
+  </si>
+  <si>
+    <t>战斗结果类型</t>
+  </si>
+  <si>
+    <t>Victory</t>
+  </si>
+  <si>
+    <t>胜利</t>
+  </si>
+  <si>
+    <t>所有敌人阵亡。</t>
+  </si>
+  <si>
+    <t>AllEscaped</t>
+  </si>
+  <si>
+    <t>全部逃脱</t>
+  </si>
+  <si>
+    <t>所有玩家成功逃跑，且没有玩家阵亡。</t>
+  </si>
+  <si>
+    <t>PartialEscapeDefeat</t>
+  </si>
+  <si>
+    <t>部分逃脱失败</t>
+  </si>
+  <si>
+    <t>至少一名玩家逃跑，其余仍在战斗中的玩家全部阵亡。</t>
+  </si>
+  <si>
+    <t>TotalDefeat</t>
+  </si>
+  <si>
+    <t>全部失败</t>
+  </si>
+  <si>
+    <t>所有玩家阵亡，没有任何玩家成功逃跑。</t>
+  </si>
+  <si>
+    <t>BattleFactionType</t>
+  </si>
+  <si>
+    <t>回合制阵营类型</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>敌人</t>
+  </si>
+  <si>
     <t>UIFormType</t>
   </si>
   <si>
@@ -596,7 +656,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -640,6 +700,11 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1116,155 +1181,154 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1293,19 +1357,21 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1796,988 +1862,988 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:12">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" customHeight="1" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:12">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
     </row>
     <row r="5" customHeight="1" spans="1:12">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15" t="s">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="15" t="b">
+      <c r="C5" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="15" t="b">
+      <c r="D5" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="14">
         <v>0</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
     </row>
     <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="14">
         <v>1</v>
       </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="14">
         <v>2</v>
       </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
     <row r="8" customHeight="1" spans="1:12">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="14">
         <v>3</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="14">
         <v>4</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" customHeight="1" spans="1:12">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="14">
         <v>5</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
     </row>
     <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="15" t="b">
+      <c r="C12" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="15" t="b">
+      <c r="D12" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="14">
         <v>0</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
     </row>
     <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="14">
         <v>1</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15" t="s">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="14">
         <v>2</v>
       </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14" t="s">
         <v>43</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>3</v>
       </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
     </row>
     <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
     </row>
     <row r="17" customHeight="1" spans="1:12">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="15" t="b">
+      <c r="C17" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="b">
+      <c r="D17" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="14">
         <v>0</v>
       </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
     </row>
     <row r="18" customHeight="1" spans="1:12">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14" t="s">
         <v>47</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="14">
         <v>1</v>
       </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
     </row>
     <row r="19" customHeight="1" spans="1:12">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14" t="s">
         <v>49</v>
       </c>
       <c r="I19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="14">
         <v>2</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
     </row>
     <row r="20" customHeight="1" spans="1:12">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
     </row>
     <row r="21" customHeight="1" spans="1:12">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="15" t="b">
+      <c r="C21" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D21" s="15" t="b">
+      <c r="D21" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="14">
         <v>0</v>
       </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
     </row>
     <row r="22" customHeight="1" spans="1:12">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15" t="s">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14" t="s">
         <v>53</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <v>1</v>
       </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
     </row>
     <row r="23" customHeight="1" spans="1:12">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14" t="s">
         <v>55</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="14">
         <v>2</v>
       </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" customHeight="1" spans="1:12">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14" t="s">
         <v>57</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="14">
         <v>3</v>
       </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
     </row>
     <row r="25" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" customHeight="1" spans="1:12">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
     </row>
     <row r="28" customHeight="1" spans="1:12">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15" t="s">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="15" t="b">
+      <c r="C28" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="15" t="b">
+      <c r="D28" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="14">
         <v>0</v>
       </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
     </row>
     <row r="29" customHeight="1" spans="1:12">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15" t="s">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14" t="s">
         <v>61</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <v>1</v>
       </c>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
     </row>
     <row r="30" customHeight="1" spans="1:12">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15" t="s">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14" t="s">
         <v>63</v>
       </c>
       <c r="I30" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="14">
         <v>2</v>
       </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
     </row>
     <row r="31" customHeight="1" spans="1:12">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15" t="s">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14" t="s">
         <v>65</v>
       </c>
       <c r="I31" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>3</v>
       </c>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
     </row>
     <row r="32" customHeight="1" spans="1:12">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14" t="s">
         <v>67</v>
       </c>
       <c r="I32" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="14">
         <v>4</v>
       </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" customHeight="1" spans="1:12">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15" t="s">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14" t="s">
         <v>69</v>
       </c>
       <c r="I33" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="14">
         <v>5</v>
       </c>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" customHeight="1" spans="1:12">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15" t="s">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14" t="s">
         <v>71</v>
       </c>
       <c r="I34" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="14">
         <v>6</v>
       </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" customHeight="1" spans="1:12">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14" t="s">
         <v>73</v>
       </c>
       <c r="I35" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="14">
         <v>7</v>
       </c>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" customHeight="1" spans="1:12">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" customHeight="1" spans="1:12">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
     </row>
     <row r="39" customHeight="1" spans="1:12">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15" t="s">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="15" t="b">
+      <c r="C39" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D39" s="15" t="b">
+      <c r="D39" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F39" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H39" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I39" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>0</v>
       </c>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
     </row>
     <row r="40" customHeight="1" spans="1:12">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14" t="s">
         <v>77</v>
       </c>
       <c r="I40" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>1</v>
       </c>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
     </row>
     <row r="41" customHeight="1" spans="1:12">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
     </row>
     <row r="42" customHeight="1" spans="1:12">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15" t="s">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C42" s="15" t="b">
+      <c r="C42" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D42" s="15" t="b">
+      <c r="D42" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I42" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>0</v>
       </c>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
     </row>
     <row r="43" customHeight="1" spans="1:12">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15" t="s">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14" t="s">
         <v>81</v>
       </c>
       <c r="I43" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>1</v>
       </c>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
     </row>
     <row r="44" customHeight="1" spans="1:12">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15" t="s">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14" t="s">
         <v>83</v>
       </c>
       <c r="I44" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>2</v>
       </c>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
     </row>
     <row r="45" customHeight="1" spans="1:12">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15" t="s">
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14" t="s">
         <v>85</v>
       </c>
       <c r="I45" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>3</v>
       </c>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
     </row>
     <row r="46" customHeight="1" spans="1:12">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15" t="s">
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14" t="s">
         <v>87</v>
       </c>
       <c r="I46" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="14">
         <v>4</v>
       </c>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
     </row>
     <row r="47" customHeight="1" spans="1:12">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
     </row>
     <row r="49" customHeight="1" spans="2:10">
       <c r="B49" s="1" t="s">
@@ -2792,7 +2858,7 @@
       <c r="E49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="11" t="s">
         <v>90</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -2801,7 +2867,7 @@
       <c r="H49" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I49" s="14" t="s">
+      <c r="I49" s="11" t="s">
         <v>92</v>
       </c>
       <c r="J49" s="1">
@@ -2812,7 +2878,7 @@
       <c r="H50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I50" s="14" t="s">
+      <c r="I50" s="11" t="s">
         <v>94</v>
       </c>
       <c r="J50" s="1">
@@ -2823,7 +2889,7 @@
       <c r="H51" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I51" s="14" t="s">
+      <c r="I51" s="11" t="s">
         <v>96</v>
       </c>
       <c r="J51" s="1">
@@ -2842,147 +2908,151 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="8.94117647058824" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="21.5661764705882" customWidth="1"/>
-    <col min="3" max="3" width="17.5220588235294" customWidth="1"/>
-    <col min="4" max="4" width="17.4044117647059" customWidth="1"/>
-    <col min="6" max="6" width="15.0735294117647" customWidth="1"/>
-    <col min="7" max="7" width="23.2867647058824" customWidth="1"/>
-    <col min="8" max="8" width="15.6838235294118" customWidth="1"/>
-    <col min="9" max="9" width="11.6397058823529" customWidth="1"/>
-    <col min="11" max="11" width="10.5367647058824" customWidth="1"/>
-    <col min="12" max="12" width="10.1691176470588" customWidth="1"/>
+    <col min="1" max="1" width="8.94117647058824" style="12"/>
+    <col min="2" max="2" width="21.5661764705882" style="12" customWidth="1"/>
+    <col min="3" max="3" width="17.5220588235294" style="12" customWidth="1"/>
+    <col min="4" max="4" width="17.4044117647059" style="12" customWidth="1"/>
+    <col min="5" max="5" width="8.94117647058824" style="12"/>
+    <col min="6" max="6" width="15.0735294117647" style="12" customWidth="1"/>
+    <col min="7" max="7" width="23.2867647058824" style="12" customWidth="1"/>
+    <col min="8" max="8" width="23.0367647058824" style="12" customWidth="1"/>
+    <col min="9" max="9" width="11.6397058823529" style="12" customWidth="1"/>
+    <col min="10" max="10" width="8.81617647058824" style="13" customWidth="1"/>
+    <col min="11" max="11" width="32.2279411764706" style="12" customWidth="1"/>
+    <col min="12" max="12" width="10.1691176470588" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="8.94117647058824" style="12"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
+      <c r="I1" s="4"/>
       <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="15" t="b">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="15" t="b">
+      <c r="D5" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="16" t="s">
@@ -2991,110 +3061,110 @@
       <c r="J5" s="15">
         <v>0</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15" t="s">
-        <v>99</v>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
+        <v>100</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J6" s="15">
         <v>1</v>
       </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15" t="s">
-        <v>101</v>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J7" s="15">
         <v>2</v>
       </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15" t="s">
-        <v>103</v>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J8" s="15">
         <v>3</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15" t="s">
-        <v>105</v>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J9" s="15">
         <v>4</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="15" t="b">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="15" t="b">
+      <c r="D12" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I12" s="16" t="s">
@@ -3103,130 +3173,130 @@
       <c r="J12" s="15">
         <v>0</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15" t="s">
-        <v>109</v>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J13" s="15">
         <v>1</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15" t="s">
-        <v>111</v>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="15">
         <v>2</v>
       </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15" t="s">
-        <v>113</v>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J15" s="15">
         <v>3</v>
       </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15" t="s">
-        <v>115</v>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J16" s="15">
         <v>4</v>
       </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15" t="s">
-        <v>117</v>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14" t="s">
+        <v>118</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J17" s="15">
         <v>5</v>
       </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="15" t="b">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="D20" s="15" t="b">
+      <c r="D20" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="14" t="s">
         <v>22</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="G20" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I20" s="16" t="s">
@@ -3235,28 +3305,144 @@
       <c r="J20" s="15">
         <v>0</v>
       </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15" t="s">
-        <v>121</v>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J21" s="15">
         <v>1</v>
       </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:12">
+      <c r="B25" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="15">
+        <v>0</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="J26" s="15">
+        <v>1</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
+      <c r="H27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J27" s="13">
+        <v>2</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
+      <c r="H28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J28" s="13">
+        <v>3</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
+      <c r="B30" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="J30" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
+      <c r="H31" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="J31" s="13">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3273,206 +3459,206 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="8.94117647058824" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.94117647058824" style="2"/>
-    <col min="2" max="2" width="22.5514705882353" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.3823529411765" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.0514705882353" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.4117647058824" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.9044117647059" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.1544117647059" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5441176470588" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.7426470588235" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.6397058823529" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.5955882352941" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.94117647058824" style="2"/>
+    <col min="1" max="1" width="8.94117647058824" style="1"/>
+    <col min="2" max="2" width="22.5514705882353" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.3823529411765" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.0514705882353" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.4117647058824" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.9044117647059" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1544117647059" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5441176470588" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7426470588235" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6397058823529" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5955882352941" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.94117647058824" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="12" t="b">
+        <v>144</v>
+      </c>
+      <c r="C5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="b">
+      <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>125</v>
+      <c r="F5" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>127</v>
+        <v>146</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>147</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
       <c r="H6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>129</v>
+        <v>148</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>131</v>
+        <v>150</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="J7" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>133</v>
+        <v>152</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>153</v>
       </c>
       <c r="J8" s="1">
         <v>101</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
       <c r="H9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>135</v>
+        <v>154</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="J9" s="1">
         <v>102</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
       <c r="H10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>137</v>
+        <v>156</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="J10" s="1">
         <v>103</v>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660" activeTab="1"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="157">
   <si>
     <t>##var</t>
   </si>
@@ -342,6 +342,198 @@
     <t>速度</t>
   </si>
   <si>
+    <t>RunResultType</t>
+  </si>
+  <si>
+    <t>单局结算类型</t>
+  </si>
+  <si>
+    <t>Extracted</t>
+  </si>
+  <si>
+    <t>成功撤离</t>
+  </si>
+  <si>
+    <t>Defeated</t>
+  </si>
+  <si>
+    <t>全员阵亡</t>
+  </si>
+  <si>
+    <t>TimedOut</t>
+  </si>
+  <si>
+    <t>超时失败</t>
+  </si>
+  <si>
+    <t>Quit</t>
+  </si>
+  <si>
+    <t>主动退出</t>
+  </si>
+  <si>
+    <t>SceneType</t>
+  </si>
+  <si>
+    <t>场景类型</t>
+  </si>
+  <si>
+    <t>Launch</t>
+  </si>
+  <si>
+    <t>启动场景</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>菜单场景</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>主场景</t>
+  </si>
+  <si>
+    <t>BattleActionType</t>
+  </si>
+  <si>
+    <t>战斗行动类型</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>Escape</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>BattleTargetType</t>
+  </si>
+  <si>
+    <t>战斗目标类型</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>自己</t>
+  </si>
+  <si>
+    <t>SingleAlly</t>
+  </si>
+  <si>
+    <t>单个友方</t>
+  </si>
+  <si>
+    <t>AllAllies</t>
+  </si>
+  <si>
+    <t>全体友方</t>
+  </si>
+  <si>
+    <t>SingleEnemy</t>
+  </si>
+  <si>
+    <t>单个敌方</t>
+  </si>
+  <si>
+    <t>AllEnemies</t>
+  </si>
+  <si>
+    <t>全体敌方</t>
+  </si>
+  <si>
+    <t>BattleStateType</t>
+  </si>
+  <si>
+    <t>战斗状态类型</t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>BattleOutcomeType</t>
+  </si>
+  <si>
+    <t>战斗结果类型</t>
+  </si>
+  <si>
+    <t>Victory</t>
+  </si>
+  <si>
+    <t>胜利</t>
+  </si>
+  <si>
+    <t>所有敌人阵亡。</t>
+  </si>
+  <si>
+    <t>AllEscaped</t>
+  </si>
+  <si>
+    <t>全部逃脱</t>
+  </si>
+  <si>
+    <t>所有玩家成功逃跑，且没有玩家阵亡。</t>
+  </si>
+  <si>
+    <t>PartialEscapeDefeat</t>
+  </si>
+  <si>
+    <t>部分逃脱失败</t>
+  </si>
+  <si>
+    <t>至少一名玩家逃跑，其余仍在战斗中的玩家全部阵亡。</t>
+  </si>
+  <si>
+    <t>TotalDefeat</t>
+  </si>
+  <si>
+    <t>全部失败</t>
+  </si>
+  <si>
+    <t>所有玩家阵亡，没有任何玩家成功逃跑。</t>
+  </si>
+  <si>
+    <t>BattleFactionType</t>
+  </si>
+  <si>
+    <t>回合制阵营类型</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>敌人</t>
+  </si>
+  <si>
     <t>EnemyAiType</t>
   </si>
   <si>
@@ -378,230 +570,6 @@
   </si>
   <si>
     <t>随机行动</t>
-  </si>
-  <si>
-    <t>RunResultType</t>
-  </si>
-  <si>
-    <t>单局结算类型</t>
-  </si>
-  <si>
-    <t>Extracted</t>
-  </si>
-  <si>
-    <t>成功撤离</t>
-  </si>
-  <si>
-    <t>Defeated</t>
-  </si>
-  <si>
-    <t>全员阵亡</t>
-  </si>
-  <si>
-    <t>TimedOut</t>
-  </si>
-  <si>
-    <t>超时失败</t>
-  </si>
-  <si>
-    <t>Quit</t>
-  </si>
-  <si>
-    <t>主动退出</t>
-  </si>
-  <si>
-    <t>SceneType</t>
-  </si>
-  <si>
-    <t>场景类型</t>
-  </si>
-  <si>
-    <t>Launch</t>
-  </si>
-  <si>
-    <t>启动场景</t>
-  </si>
-  <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <t>菜单场景</t>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <t>主场景</t>
-  </si>
-  <si>
-    <r>
-      <t>全名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>包含模块和名字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>BattleActionType</t>
-  </si>
-  <si>
-    <t>战斗行动类型</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>道具</t>
-  </si>
-  <si>
-    <t>Escape</t>
-  </si>
-  <si>
-    <t>逃跑</t>
-  </si>
-  <si>
-    <t>BattleTargetType</t>
-  </si>
-  <si>
-    <t>战斗目标类型</t>
-  </si>
-  <si>
-    <t>Self</t>
-  </si>
-  <si>
-    <t>自己</t>
-  </si>
-  <si>
-    <t>SingleAlly</t>
-  </si>
-  <si>
-    <t>单个友方</t>
-  </si>
-  <si>
-    <t>AllAllies</t>
-  </si>
-  <si>
-    <t>全体友方</t>
-  </si>
-  <si>
-    <t>SingleEnemy</t>
-  </si>
-  <si>
-    <t>单个敌方</t>
-  </si>
-  <si>
-    <t>AllEnemies</t>
-  </si>
-  <si>
-    <t>全体敌方</t>
-  </si>
-  <si>
-    <t>BattleStateType</t>
-  </si>
-  <si>
-    <t>战斗状态类型</t>
-  </si>
-  <si>
-    <t>Stun</t>
-  </si>
-  <si>
-    <t>眩晕</t>
-  </si>
-  <si>
-    <t>BattleOutcomeType</t>
-  </si>
-  <si>
-    <t>战斗结果类型</t>
-  </si>
-  <si>
-    <t>Victory</t>
-  </si>
-  <si>
-    <t>胜利</t>
-  </si>
-  <si>
-    <t>所有敌人阵亡。</t>
-  </si>
-  <si>
-    <t>AllEscaped</t>
-  </si>
-  <si>
-    <t>全部逃脱</t>
-  </si>
-  <si>
-    <t>所有玩家成功逃跑，且没有玩家阵亡。</t>
-  </si>
-  <si>
-    <t>PartialEscapeDefeat</t>
-  </si>
-  <si>
-    <t>部分逃脱失败</t>
-  </si>
-  <si>
-    <t>至少一名玩家逃跑，其余仍在战斗中的玩家全部阵亡。</t>
-  </si>
-  <si>
-    <t>TotalDefeat</t>
-  </si>
-  <si>
-    <t>全部失败</t>
-  </si>
-  <si>
-    <t>所有玩家阵亡，没有任何玩家成功逃跑。</t>
-  </si>
-  <si>
-    <t>BattleFactionType</t>
-  </si>
-  <si>
-    <t>回合制阵营类型</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>玩家</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>敌人</t>
   </si>
   <si>
     <t>UIFormType</t>
@@ -1327,7 +1295,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1358,10 +1326,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1846,7 +1810,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1954,945 +1918,879 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:12">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" customHeight="1" spans="1:12">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="14" t="b">
+      <c r="C5" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="b">
+      <c r="D5" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="12">
         <v>0</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <v>1</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="12">
         <v>2</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" customHeight="1" spans="1:12">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="12">
         <v>3</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
     </row>
     <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="12">
         <v>4</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
     </row>
     <row r="10" customHeight="1" spans="1:12">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="12">
         <v>5</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
     </row>
     <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="14" t="b">
+      <c r="C12" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="14" t="b">
+      <c r="D12" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="12">
         <v>0</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="12">
         <v>1</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
     </row>
     <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14" t="s">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="12">
         <v>2</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="12">
         <v>3</v>
       </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
     </row>
     <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
     </row>
     <row r="17" customHeight="1" spans="1:12">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="14" t="b">
+      <c r="C17" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="14" t="b">
+      <c r="D17" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="12">
         <v>0</v>
       </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
     </row>
     <row r="18" customHeight="1" spans="1:12">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="12">
         <v>1</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19" customHeight="1" spans="1:12">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="16" t="s">
+      <c r="I19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="12">
         <v>2</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="20" customHeight="1" spans="1:12">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
     </row>
     <row r="21" customHeight="1" spans="1:12">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="14" t="b">
+      <c r="C21" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D21" s="14" t="b">
+      <c r="D21" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="16" t="s">
+      <c r="I21" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="12">
         <v>0</v>
       </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
     </row>
     <row r="22" customHeight="1" spans="1:12">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14" t="s">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="I22" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="12">
         <v>1</v>
       </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
     </row>
     <row r="23" customHeight="1" spans="1:12">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14" t="s">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="12">
         <v>2</v>
       </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
     </row>
     <row r="24" customHeight="1" spans="1:12">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14" t="s">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I24" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="12">
         <v>3</v>
       </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
     </row>
     <row r="25" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27" customHeight="1" spans="1:12">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
     </row>
     <row r="28" customHeight="1" spans="1:12">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14" t="s">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="14" t="b">
+      <c r="C28" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="14" t="b">
+      <c r="D28" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="H28" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="16" t="s">
+      <c r="I28" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="12">
         <v>0</v>
       </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
     </row>
     <row r="29" customHeight="1" spans="1:12">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14" t="s">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="12">
         <v>1</v>
       </c>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
     </row>
     <row r="30" customHeight="1" spans="1:12">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14" t="s">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I30" s="16" t="s">
+      <c r="I30" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="12">
         <v>2</v>
       </c>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
     </row>
     <row r="31" customHeight="1" spans="1:12">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14" t="s">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="12">
         <v>3</v>
       </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
     </row>
     <row r="32" customHeight="1" spans="1:12">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14" t="s">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="J32" s="14">
+      <c r="J32" s="12">
         <v>4</v>
       </c>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
     </row>
     <row r="33" customHeight="1" spans="1:12">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14" t="s">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="12">
         <v>5</v>
       </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
     </row>
     <row r="34" customHeight="1" spans="1:12">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14" t="s">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="I34" s="16" t="s">
+      <c r="I34" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="12">
         <v>6</v>
       </c>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
     </row>
     <row r="35" customHeight="1" spans="1:12">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14" t="s">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="12">
         <v>7</v>
       </c>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
     </row>
     <row r="36" customHeight="1" spans="1:12">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
     </row>
     <row r="37" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
     </row>
     <row r="38" customHeight="1" spans="1:12">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
     </row>
     <row r="39" customHeight="1" spans="1:12">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14" t="s">
+      <c r="A39" s="12"/>
+      <c r="B39" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="14" t="b">
+      <c r="C39" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D39" s="14" t="b">
+      <c r="D39" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="H39" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I39" s="16" t="s">
+      <c r="I39" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="14">
+      <c r="J39" s="12">
         <v>0</v>
       </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
     </row>
     <row r="40" customHeight="1" spans="1:12">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14" t="s">
+      <c r="A40" s="12"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="I40" s="16" t="s">
+      <c r="I40" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="J40" s="14">
+      <c r="J40" s="12">
         <v>1</v>
       </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
     </row>
     <row r="41" customHeight="1" spans="1:12">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="12">
+        <v>2</v>
+      </c>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
     </row>
     <row r="42" customHeight="1" spans="1:12">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="14" t="b">
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J42" s="12">
+        <v>3</v>
+      </c>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:12">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J43" s="12">
+        <v>4</v>
+      </c>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:12">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:12">
+      <c r="B46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" s="1">
         <v>0</v>
       </c>
-      <c r="D42" s="14" t="b">
+      <c r="D46" s="1">
         <v>1</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G42" s="14" t="s">
+      <c r="F46" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H42" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I42" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J42" s="14">
+      <c r="H46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J46" s="1">
         <v>0</v>
       </c>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:12">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="J43" s="14">
+    </row>
+    <row r="47" customHeight="1" spans="1:12">
+      <c r="H47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="J47" s="1">
         <v>1</v>
       </c>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:12">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="I44" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="J44" s="14">
-        <v>2</v>
-      </c>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:12">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I45" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="J45" s="14">
-        <v>3</v>
-      </c>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:12">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I46" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="J46" s="14">
-        <v>4</v>
-      </c>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:12">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-    </row>
-    <row r="49" customHeight="1" spans="2:10">
-      <c r="B49" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="1" t="s">
+    </row>
+    <row r="48" customHeight="1" spans="1:12">
+      <c r="H48" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I48" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="2:10">
-      <c r="H50" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="J50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="2:10">
-      <c r="H51" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="J51" s="1">
+      <c r="J48" s="1">
         <v>2</v>
       </c>
     </row>
@@ -2908,22 +2806,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="8.94117647058824" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.94117647058824" style="12"/>
-    <col min="2" max="2" width="21.5661764705882" style="12" customWidth="1"/>
-    <col min="3" max="3" width="17.5220588235294" style="12" customWidth="1"/>
-    <col min="4" max="4" width="17.4044117647059" style="12" customWidth="1"/>
-    <col min="5" max="5" width="8.94117647058824" style="12"/>
-    <col min="6" max="6" width="15.0735294117647" style="12" customWidth="1"/>
-    <col min="7" max="7" width="23.2867647058824" style="12" customWidth="1"/>
-    <col min="8" max="8" width="23.0367647058824" style="12" customWidth="1"/>
-    <col min="9" max="9" width="11.6397058823529" style="12" customWidth="1"/>
-    <col min="10" max="10" width="8.81617647058824" style="13" customWidth="1"/>
-    <col min="11" max="11" width="32.2279411764706" style="12" customWidth="1"/>
-    <col min="12" max="12" width="10.1691176470588" style="12" customWidth="1"/>
-    <col min="13" max="16384" width="8.94117647058824" style="12"/>
+    <col min="1" max="1" width="8.94117647058824" style="1"/>
+    <col min="2" max="2" width="21.5661764705882" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5220588235294" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.4044117647059" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.94117647058824" style="1"/>
+    <col min="6" max="6" width="15.0735294117647" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.2867647058824" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.0367647058824" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6397058823529" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.81617647058824" style="2" customWidth="1"/>
+    <col min="11" max="11" width="32.2279411764706" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1691176470588" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.94117647058824" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
@@ -2987,7 +2885,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>13</v>
@@ -3019,430 +2917,482 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="13">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="14" t="b">
+      <c r="J7" s="13">
+        <v>2</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="J8" s="13">
+        <v>3</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="13">
+        <v>4</v>
+      </c>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="b">
+      <c r="D12" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="F12" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I12" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J12" s="13">
         <v>0</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="J6" s="15">
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="13">
         <v>1</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="J7" s="15">
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="13">
         <v>2</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="15">
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J15" s="13">
         <v>3</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="15">
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J16" s="13">
         <v>4</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="14" t="b">
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="13">
+        <v>5</v>
+      </c>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="14" t="b">
+      <c r="D20" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E20" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F20" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J20" s="13">
         <v>0</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="J13" s="15">
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21" s="13">
         <v>1</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="15">
-        <v>2</v>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="J16" s="15">
-        <v>4</v>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" s="15">
-        <v>5</v>
-      </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="15">
-        <v>0</v>
-      </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="J21" s="15">
-        <v>1</v>
-      </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
     </row>
     <row r="25" customHeight="1" spans="1:12">
       <c r="B25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="J25" s="13">
+        <v>0</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="14" t="b">
+      <c r="I26" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="J26" s="13">
         <v>1</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="14" t="s">
+      <c r="K26" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="J25" s="15">
-        <v>0</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="J26" s="15">
-        <v>1</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:12">
       <c r="H27" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="J27" s="13">
+        <v>128</v>
+      </c>
+      <c r="J27" s="2">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:12">
       <c r="H28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="J28" s="2">
+        <v>3</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
+      <c r="B30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I30" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="J28" s="13">
-        <v>3</v>
-      </c>
-      <c r="K28" s="11" t="s">
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
+      <c r="H31" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
-      <c r="B30" s="12" t="s">
+      <c r="I31" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C30" s="14" t="b">
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D30" s="14" t="b">
+      <c r="D34" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E34" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F34" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H30" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="I30" s="17" t="s">
+      <c r="H34" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="12">
+        <v>0</v>
+      </c>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="J30" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:12">
-      <c r="H31" s="12" t="s">
+      <c r="I35" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="I31" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="J31" s="13">
+      <c r="J35" s="12">
         <v>1</v>
       </c>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3567,7 +3517,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>0</v>
@@ -3579,16 +3529,16 @@
         <v>22</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>146</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>147</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -3599,10 +3549,10 @@
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="H6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -3613,10 +3563,10 @@
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="H7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>151</v>
       </c>
       <c r="J7" s="1">
         <v>100</v>
@@ -3627,10 +3577,10 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="H8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>152</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>153</v>
       </c>
       <c r="J8" s="1">
         <v>101</v>
@@ -3641,10 +3591,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
       <c r="H9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>155</v>
       </c>
       <c r="J9" s="1">
         <v>102</v>
@@ -3655,10 +3605,10 @@
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="H10" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>156</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>157</v>
       </c>
       <c r="J10" s="1">
         <v>103</v>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowHeight="16660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660" activeTab="1"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="165">
   <si>
     <t>##var</t>
   </si>
@@ -394,6 +394,30 @@
   </si>
   <si>
     <t>主场景</t>
+  </si>
+  <si>
+    <t>EnemyPartyThreatLevel</t>
+  </si>
+  <si>
+    <t>敌人队伍威胁等级</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>高</t>
   </si>
   <si>
     <t>BattleActionType</t>
@@ -1810,7 +1834,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -2792,6 +2816,68 @@
       </c>
       <c r="J48" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="2:10">
+      <c r="B51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="2:10">
+      <c r="H52" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="2:10">
+      <c r="H53" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="2:10">
+      <c r="H54" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="J54" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2933,7 +3019,7 @@
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A5" s="12"/>
       <c r="B5" s="12" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -2945,7 +3031,7 @@
         <v>22</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>24</v>
@@ -2971,10 +3057,10 @@
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="J6" s="13">
         <v>1</v>
@@ -2991,10 +3077,10 @@
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J7" s="13">
         <v>2</v>
@@ -3011,10 +3097,10 @@
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J8" s="13">
         <v>3</v>
@@ -3031,10 +3117,10 @@
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J9" s="13">
         <v>4</v>
@@ -3045,7 +3131,7 @@
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A12" s="12"/>
       <c r="B12" s="12" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -3057,7 +3143,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>24</v>
@@ -3083,10 +3169,10 @@
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J13" s="13">
         <v>1</v>
@@ -3103,10 +3189,10 @@
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J14" s="13">
         <v>2</v>
@@ -3123,10 +3209,10 @@
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J15" s="13">
         <v>3</v>
@@ -3143,10 +3229,10 @@
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="J16" s="13">
         <v>4</v>
@@ -3163,10 +3249,10 @@
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J17" s="13">
         <v>5</v>
@@ -3177,7 +3263,7 @@
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A20" s="12"/>
       <c r="B20" s="12" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C20" s="12" t="b">
         <v>0</v>
@@ -3189,7 +3275,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>24</v>
@@ -3215,10 +3301,10 @@
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J21" s="13">
         <v>1</v>
@@ -3228,7 +3314,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:12">
       <c r="B25" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C25" s="12" t="b">
         <v>0</v>
@@ -3240,71 +3326,71 @@
         <v>22</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G25" s="12" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J25" s="13">
         <v>0</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:12">
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J26" s="13">
         <v>1</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:12">
       <c r="H27" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J27" s="2">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:12">
       <c r="H28" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="J28" s="2">
         <v>3</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:12">
       <c r="B30" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C30" s="12" t="b">
         <v>0</v>
@@ -3316,16 +3402,16 @@
         <v>22</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -3333,10 +3419,10 @@
     </row>
     <row r="31" customHeight="1" spans="1:12">
       <c r="H31" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J31" s="2">
         <v>1</v>
@@ -3345,7 +3431,7 @@
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A34" s="12"/>
       <c r="B34" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C34" s="12" t="b">
         <v>0</v>
@@ -3357,7 +3443,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>24</v>
@@ -3383,10 +3469,10 @@
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J35" s="12">
         <v>1</v>
@@ -3517,7 +3603,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>0</v>
@@ -3529,16 +3615,16 @@
         <v>22</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -3549,10 +3635,10 @@
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="H6" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -3563,10 +3649,10 @@
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="J7" s="1">
         <v>100</v>
@@ -3577,10 +3663,10 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J8" s="1">
         <v>101</v>
@@ -3591,10 +3677,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
       <c r="H9" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J9" s="1">
         <v>102</v>
@@ -3605,10 +3691,10 @@
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="H10" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="J10" s="1">
         <v>103</v>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
   <si>
     <t>##var</t>
   </si>
@@ -65,6 +70,713 @@
   </si>
   <si>
     <t>##</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包含模块和名字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否为位标记枚举</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>枚举项是否唯一</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注释</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>枚举级标签</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>枚举名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>别名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>枚举项标签</t>
+    </r>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>稀有度</t>
+    </r>
+  </si>
+  <si>
+    <t>cs_underlying=byte</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无</t>
+    </r>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>白</t>
+    </r>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绿</t>
+    </r>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蓝</t>
+    </r>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金</t>
+    </r>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>红</t>
+    </r>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>物品类型</t>
+    </r>
+  </si>
+  <si>
+    <t>Loot</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战利品</t>
+    </r>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>装备</t>
+    </r>
+  </si>
+  <si>
+    <t>Consumable</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>消耗品</t>
+    </r>
+  </si>
+  <si>
+    <t>EquipmentSlotType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>装备栏类型</t>
+    </r>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武器</t>
+    </r>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>防具</t>
+    </r>
+  </si>
+  <si>
+    <t>DifficultyTier</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难度档位</t>
+    </r>
+  </si>
+  <si>
+    <t>Tier1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Tier2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>Tier3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleStatType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗属性类型</t>
+    </r>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前生命</t>
+    </r>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前魔力</t>
+    </r>
+  </si>
+  <si>
+    <t>MaxHP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生命上限</t>
+    </r>
+  </si>
+  <si>
+    <t>MaxMP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔力上限</t>
+    </r>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力</t>
+    </r>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔力</t>
+    </r>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>速度</t>
+    </r>
+  </si>
+  <si>
+    <t>RunResultType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单局结算类型</t>
+    </r>
+  </si>
+  <si>
+    <t>Extracted</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成功撤离</t>
+    </r>
+  </si>
+  <si>
+    <t>Defeated</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全员阵亡</t>
+    </r>
+  </si>
+  <si>
+    <t>TimedOut</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>超时失败</t>
+    </r>
+  </si>
+  <si>
+    <t>Quit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主动退出</t>
+    </r>
+  </si>
+  <si>
+    <t>SceneType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>场景类型</t>
+    </r>
+  </si>
+  <si>
+    <t>Launch</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启动场景</t>
+    </r>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜单场景</t>
+    </r>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主场景</t>
+    </r>
+  </si>
+  <si>
+    <t>EnemyPartyThreatLevel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人队伍威胁等级</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无</t>
+    </r>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低</t>
+    </r>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
   </si>
   <si>
     <r>
@@ -129,103 +841,148 @@
     <t>枚举项标签</t>
   </si>
   <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>稀有度</t>
-  </si>
-  <si>
-    <t>cs_underlying=byte</t>
-  </si>
-  <si>
-    <t>None</t>
+    <t>BattleActionType</t>
+  </si>
+  <si>
+    <t>战斗行动类型</t>
   </si>
   <si>
     <t>无</t>
   </si>
   <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>绿</t>
-  </si>
-  <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>金</t>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>物品类型</t>
-  </si>
-  <si>
-    <t>Loot</t>
-  </si>
-  <si>
-    <t>战利品</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>装备</t>
-  </si>
-  <si>
-    <t>Consumable</t>
-  </si>
-  <si>
-    <t>消耗品</t>
-  </si>
-  <si>
-    <t>EquipmentSlotType</t>
-  </si>
-  <si>
-    <t>装备栏类型</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>武器</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>防具</t>
-  </si>
-  <si>
-    <t>DifficultyTier</t>
-  </si>
-  <si>
-    <t>难度档位</t>
-  </si>
-  <si>
-    <t>Tier1</t>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>Escape</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>BattleTargetType</t>
+  </si>
+  <si>
+    <t>战斗目标类型</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>自己</t>
+  </si>
+  <si>
+    <t>SingleAlly</t>
+  </si>
+  <si>
+    <t>单个友方</t>
+  </si>
+  <si>
+    <t>AllAllies</t>
+  </si>
+  <si>
+    <t>全体友方</t>
+  </si>
+  <si>
+    <t>SingleEnemy</t>
+  </si>
+  <si>
+    <t>单个敌方</t>
+  </si>
+  <si>
+    <t>AllEnemies</t>
+  </si>
+  <si>
+    <t>全体敌方</t>
+  </si>
+  <si>
+    <t>BattleStateType</t>
+  </si>
+  <si>
+    <t>战斗状态类型</t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>BattleOutcomeType</t>
+  </si>
+  <si>
+    <t>战斗结果类型</t>
+  </si>
+  <si>
+    <t>Victory</t>
+  </si>
+  <si>
+    <t>胜利</t>
+  </si>
+  <si>
+    <t>所有敌人阵亡。</t>
+  </si>
+  <si>
+    <t>AllEscaped</t>
+  </si>
+  <si>
+    <t>全部逃脱</t>
+  </si>
+  <si>
+    <t>所有玩家成功逃跑，且没有玩家阵亡。</t>
+  </si>
+  <si>
+    <t>PartialEscapeDefeat</t>
+  </si>
+  <si>
+    <t>部分逃脱失败</t>
+  </si>
+  <si>
+    <t>至少一名玩家逃跑，其余仍在战斗中的玩家全部阵亡。</t>
+  </si>
+  <si>
+    <t>TotalDefeat</t>
+  </si>
+  <si>
+    <t>全部失败</t>
+  </si>
+  <si>
+    <t>所有玩家阵亡，没有任何玩家成功逃跑。</t>
+  </si>
+  <si>
+    <t>BattleFactionType</t>
+  </si>
+  <si>
+    <t>回合制阵营类型</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>敌人</t>
+  </si>
+  <si>
+    <t>EnemyAiType</t>
   </si>
   <si>
     <r>
@@ -235,7 +992,7 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>难度</t>
+      <t>敌人</t>
     </r>
     <r>
       <rPr>
@@ -244,13 +1001,8 @@
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>Tier2</t>
-  </si>
-  <si>
+      <t>AI</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -258,334 +1010,6 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>难度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>Tier3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>难度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>BattleStatType</t>
-  </si>
-  <si>
-    <t>战斗属性类型</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>当前生命</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>当前魔力</t>
-  </si>
-  <si>
-    <t>MaxHP</t>
-  </si>
-  <si>
-    <t>生命上限</t>
-  </si>
-  <si>
-    <t>MaxMP</t>
-  </si>
-  <si>
-    <t>魔力上限</t>
-  </si>
-  <si>
-    <t>ATK</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>MAT</t>
-  </si>
-  <si>
-    <t>魔力</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>速度</t>
-  </si>
-  <si>
-    <t>RunResultType</t>
-  </si>
-  <si>
-    <t>单局结算类型</t>
-  </si>
-  <si>
-    <t>Extracted</t>
-  </si>
-  <si>
-    <t>成功撤离</t>
-  </si>
-  <si>
-    <t>Defeated</t>
-  </si>
-  <si>
-    <t>全员阵亡</t>
-  </si>
-  <si>
-    <t>TimedOut</t>
-  </si>
-  <si>
-    <t>超时失败</t>
-  </si>
-  <si>
-    <t>Quit</t>
-  </si>
-  <si>
-    <t>主动退出</t>
-  </si>
-  <si>
-    <t>SceneType</t>
-  </si>
-  <si>
-    <t>场景类型</t>
-  </si>
-  <si>
-    <t>Launch</t>
-  </si>
-  <si>
-    <t>启动场景</t>
-  </si>
-  <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <t>菜单场景</t>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <t>主场景</t>
-  </si>
-  <si>
-    <t>EnemyPartyThreatLevel</t>
-  </si>
-  <si>
-    <t>敌人队伍威胁等级</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>低</t>
-  </si>
-  <si>
-    <t>Middle</t>
-  </si>
-  <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>高</t>
-  </si>
-  <si>
-    <t>BattleActionType</t>
-  </si>
-  <si>
-    <t>战斗行动类型</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>道具</t>
-  </si>
-  <si>
-    <t>Escape</t>
-  </si>
-  <si>
-    <t>逃跑</t>
-  </si>
-  <si>
-    <t>BattleTargetType</t>
-  </si>
-  <si>
-    <t>战斗目标类型</t>
-  </si>
-  <si>
-    <t>Self</t>
-  </si>
-  <si>
-    <t>自己</t>
-  </si>
-  <si>
-    <t>SingleAlly</t>
-  </si>
-  <si>
-    <t>单个友方</t>
-  </si>
-  <si>
-    <t>AllAllies</t>
-  </si>
-  <si>
-    <t>全体友方</t>
-  </si>
-  <si>
-    <t>SingleEnemy</t>
-  </si>
-  <si>
-    <t>单个敌方</t>
-  </si>
-  <si>
-    <t>AllEnemies</t>
-  </si>
-  <si>
-    <t>全体敌方</t>
-  </si>
-  <si>
-    <t>BattleStateType</t>
-  </si>
-  <si>
-    <t>战斗状态类型</t>
-  </si>
-  <si>
-    <t>Stun</t>
-  </si>
-  <si>
-    <t>眩晕</t>
-  </si>
-  <si>
-    <t>BattleOutcomeType</t>
-  </si>
-  <si>
-    <t>战斗结果类型</t>
-  </si>
-  <si>
-    <t>Victory</t>
-  </si>
-  <si>
-    <t>胜利</t>
-  </si>
-  <si>
-    <t>所有敌人阵亡。</t>
-  </si>
-  <si>
-    <t>AllEscaped</t>
-  </si>
-  <si>
-    <t>全部逃脱</t>
-  </si>
-  <si>
-    <t>所有玩家成功逃跑，且没有玩家阵亡。</t>
-  </si>
-  <si>
-    <t>PartialEscapeDefeat</t>
-  </si>
-  <si>
-    <t>部分逃脱失败</t>
-  </si>
-  <si>
-    <t>至少一名玩家逃跑，其余仍在战斗中的玩家全部阵亡。</t>
-  </si>
-  <si>
-    <t>TotalDefeat</t>
-  </si>
-  <si>
-    <t>全部失败</t>
-  </si>
-  <si>
-    <t>所有玩家阵亡，没有任何玩家成功逃跑。</t>
-  </si>
-  <si>
-    <t>BattleFactionType</t>
-  </si>
-  <si>
-    <t>回合制阵营类型</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>玩家</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>敌人</t>
-  </si>
-  <si>
-    <t>EnemyAiType</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
       <t>类型</t>
     </r>
   </si>
@@ -596,6 +1020,38 @@
     <t>随机行动</t>
   </si>
   <si>
+    <r>
+      <t>全名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包含模块和名字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
     <t>UIFormType</t>
   </si>
   <si>
@@ -636,6 +1092,12 @@
   </si>
   <si>
     <t>战斗界面</t>
+  </si>
+  <si>
+    <t>JoystickForm</t>
+  </si>
+  <si>
+    <t>输入面板</t>
   </si>
 </sst>
 </file>
@@ -648,10 +1110,38 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -679,11 +1169,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
@@ -696,7 +1181,23 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -820,6 +1321,12 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1173,153 +1680,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1350,17 +1857,41 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1839,12 +2370,12 @@
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.3529411764706" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.9264705882353" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.35" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.925" style="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.4411764705882" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.7132352941176" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.0735294117647" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.4416666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.7166666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.075" style="1" customWidth="1"/>
     <col min="9" max="12" width="10" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
@@ -1909,863 +2440,863 @@
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:12">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" customHeight="1" spans="1:12">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="12" t="b">
+      <c r="C5" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="b">
+      <c r="D5" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="25">
         <v>0</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="25">
         <v>1</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="25">
         <v>2</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" customHeight="1" spans="1:12">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="25">
         <v>3</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="25">
         <v>4</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" customHeight="1" spans="1:12">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="25">
         <v>5</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="12" t="b">
+      <c r="C12" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="12" t="b">
+      <c r="D12" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="25">
         <v>0</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="25">
         <v>1</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="25">
         <v>2</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="25">
         <v>3</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" customHeight="1" spans="1:12">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="12" t="b">
+      <c r="C17" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="12" t="b">
+      <c r="D17" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="25">
         <v>0</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" customHeight="1" spans="1:12">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="25">
         <v>1</v>
       </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" customHeight="1" spans="1:12">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="25">
         <v>2</v>
       </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" customHeight="1" spans="1:12">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" customHeight="1" spans="1:12">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12" t="s">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="12" t="b">
+      <c r="C21" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D21" s="12" t="b">
+      <c r="D21" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="25">
         <v>0</v>
       </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" customHeight="1" spans="1:12">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12" t="s">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="25">
         <v>1</v>
       </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" customHeight="1" spans="1:12">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12" t="s">
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="25">
         <v>2</v>
       </c>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" customHeight="1" spans="1:12">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12" t="s">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="25">
         <v>3</v>
       </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" s="24" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+    </row>
+    <row r="26" s="24" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
     </row>
     <row r="27" customHeight="1" spans="1:12">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" customHeight="1" spans="1:12">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="12" t="b">
+      <c r="C28" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="12" t="b">
+      <c r="D28" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="25">
         <v>0</v>
       </c>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" customHeight="1" spans="1:12">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="25">
         <v>1</v>
       </c>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" customHeight="1" spans="1:12">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12" t="s">
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I30" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="25">
         <v>2</v>
       </c>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" customHeight="1" spans="1:12">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12" t="s">
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="25">
         <v>3</v>
       </c>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" customHeight="1" spans="1:12">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12" t="s">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="25">
         <v>4</v>
       </c>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" customHeight="1" spans="1:12">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12" t="s">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="25">
         <v>5</v>
       </c>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" customHeight="1" spans="1:12">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12" t="s">
+      <c r="A34" s="25"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I34" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="25">
         <v>6</v>
       </c>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" customHeight="1" spans="1:12">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12" t="s">
+      <c r="A35" s="25"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="12">
+      <c r="J35" s="25">
         <v>7</v>
       </c>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" customHeight="1" spans="1:12">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+    </row>
+    <row r="37" s="24" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
     </row>
     <row r="38" customHeight="1" spans="1:12">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
     </row>
     <row r="39" customHeight="1" spans="1:12">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12" t="s">
+      <c r="A39" s="25"/>
+      <c r="B39" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="12" t="b">
+      <c r="C39" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D39" s="12" t="b">
+      <c r="D39" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H39" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="12">
+      <c r="J39" s="25">
         <v>0</v>
       </c>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
     </row>
     <row r="40" customHeight="1" spans="1:12">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12" t="s">
+      <c r="A40" s="25"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I40" s="14" t="s">
+      <c r="I40" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="J40" s="12">
+      <c r="J40" s="25">
         <v>1</v>
       </c>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
     </row>
     <row r="41" customHeight="1" spans="1:12">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12" t="s">
+      <c r="A41" s="25"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I41" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="J41" s="12">
+      <c r="J41" s="25">
         <v>2</v>
       </c>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
     </row>
     <row r="42" customHeight="1" spans="1:12">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="I42" s="14" t="s">
+      <c r="I42" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="J42" s="12">
+      <c r="J42" s="25">
         <v>3</v>
       </c>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
     </row>
     <row r="43" customHeight="1" spans="1:12">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12" t="s">
+      <c r="A43" s="25"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="J43" s="12">
+      <c r="J43" s="25">
         <v>4</v>
       </c>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="25"/>
     </row>
     <row r="44" customHeight="1" spans="1:12">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25"/>
     </row>
     <row r="46" customHeight="1" spans="1:12">
       <c r="B46" s="1" t="s">
@@ -2780,7 +3311,7 @@
       <c r="E46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="1" t="s">
         <v>86</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -2789,7 +3320,7 @@
       <c r="H46" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J46" s="1">
@@ -2800,7 +3331,7 @@
       <c r="H47" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="J47" s="1">
@@ -2811,7 +3342,7 @@
       <c r="H48" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="1" t="s">
         <v>92</v>
       </c>
       <c r="J48" s="1">
@@ -2831,7 +3362,7 @@
       <c r="E51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="F51" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -2840,8 +3371,8 @@
       <c r="H51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I51" s="15" t="s">
-        <v>26</v>
+      <c r="I51" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
@@ -2849,10 +3380,10 @@
     </row>
     <row r="52" customHeight="1" spans="2:10">
       <c r="H52" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I52" s="15" t="s">
         <v>96</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="J52" s="1">
         <v>1</v>
@@ -2860,10 +3391,10 @@
     </row>
     <row r="53" customHeight="1" spans="2:10">
       <c r="H53" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I53" s="15" t="s">
         <v>98</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="J53" s="1">
         <v>2</v>
@@ -2871,10 +3402,10 @@
     </row>
     <row r="54" customHeight="1" spans="2:10">
       <c r="H54" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I54" s="15" t="s">
         <v>100</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="J54" s="1">
         <v>3</v>
@@ -2893,592 +3424,592 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="8.94117647058824" defaultRowHeight="20" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.94117647058824" style="1"/>
-    <col min="2" max="2" width="21.5661764705882" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5220588235294" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.4044117647059" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.94117647058824" style="1"/>
-    <col min="6" max="6" width="15.0735294117647" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.2867647058824" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.0367647058824" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6397058823529" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81617647058824" style="2" customWidth="1"/>
-    <col min="11" max="11" width="32.2279411764706" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1691176470588" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.94117647058824" style="1"/>
+    <col min="1" max="1" width="8.94166666666667" style="12"/>
+    <col min="2" max="2" width="21.5666666666667" style="12" customWidth="1"/>
+    <col min="3" max="3" width="17.525" style="12" customWidth="1"/>
+    <col min="4" max="4" width="17.4083333333333" style="12" customWidth="1"/>
+    <col min="5" max="5" width="8.94166666666667" style="12"/>
+    <col min="6" max="6" width="15.075" style="12" customWidth="1"/>
+    <col min="7" max="7" width="23.2833333333333" style="12" customWidth="1"/>
+    <col min="8" max="8" width="23.0333333333333" style="12" customWidth="1"/>
+    <col min="9" max="9" width="11.6416666666667" style="12" customWidth="1"/>
+    <col min="10" max="10" width="8.81666666666667" style="13" customWidth="1"/>
+    <col min="11" max="11" width="32.225" style="12" customWidth="1"/>
+    <col min="12" max="12" width="10.1666666666667" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="8.94166666666667" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="I1" s="14"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
+    <row r="3" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="12" t="b">
+      <c r="B3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+    </row>
+    <row r="5" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="b">
+      <c r="D5" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="12" t="s">
+      <c r="F5" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="13">
+      <c r="I5" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="20">
         <v>0</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J6" s="13">
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+    </row>
+    <row r="6" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="20">
         <v>1</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J7" s="13">
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+    </row>
+    <row r="7" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="20">
         <v>2</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="J8" s="13">
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="20">
         <v>3</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="13">
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+    </row>
+    <row r="9" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" s="20">
         <v>4</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="12" t="b">
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+    </row>
+    <row r="12" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="12" t="b">
+      <c r="D12" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="F12" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="13">
+      <c r="I12" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="20">
         <v>0</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12" t="s">
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="J13" s="20">
+        <v>1</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="20">
+        <v>2</v>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+    </row>
+    <row r="15" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="J15" s="20">
+        <v>3</v>
+      </c>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+    </row>
+    <row r="16" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="J16" s="20">
+        <v>4</v>
+      </c>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+    </row>
+    <row r="17" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="20">
+        <v>5</v>
+      </c>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+    </row>
+    <row r="20" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="J13" s="13">
+      <c r="J20" s="20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+    </row>
+    <row r="21" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" s="20">
         <v>1</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="13">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:12">
+      <c r="B25" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="J25" s="20">
+        <v>0</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="J26" s="20">
+        <v>1</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
+      <c r="H27" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="J27" s="13">
         <v>2</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="J15" s="13">
+      <c r="K27" s="22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
+      <c r="H28" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="J28" s="13">
         <v>3</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J16" s="13">
-        <v>4</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="J17" s="13">
-        <v>5</v>
-      </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="12" t="b">
+      <c r="K28" s="22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
+      <c r="B30" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="D20" s="12" t="b">
+      <c r="D30" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E30" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="G20" s="12" t="s">
+      <c r="F30" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H30" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="J30" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
+      <c r="H31" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="J31" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="13">
+      <c r="I34" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="J34" s="19">
         <v>0</v>
       </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="J21" s="13">
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="J35" s="19">
         <v>1</v>
       </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:12">
-      <c r="B25" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="J25" s="13">
-        <v>0</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="J26" s="13">
-        <v>1</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:12">
-      <c r="H27" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J27" s="2">
-        <v>2</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:12">
-      <c r="H28" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="J28" s="2">
-        <v>3</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
-      <c r="B30" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:12">
-      <c r="H31" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="12">
-        <v>0</v>
-      </c>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="J35" s="12">
-        <v>1</v>
-      </c>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3492,21 +4023,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.94117647058824" defaultRowHeight="20" customHeight="1"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.94117647058824" style="1"/>
-    <col min="2" max="2" width="22.5514705882353" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.3823529411765" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.0514705882353" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.4117647058824" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.9044117647059" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1544117647059" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5441176470588" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7426470588235" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6397058823529" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5955882352941" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.94117647058824" style="1"/>
+    <col min="1" max="1" width="8.94166666666667" style="1"/>
+    <col min="2" max="2" width="22.55" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.4083333333333" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.9083333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1583333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7416666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6416666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5916666666667" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.94166666666667" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
@@ -3570,40 +4101,40 @@
         <v>11</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="8" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>0</v>
@@ -3615,16 +4146,16 @@
         <v>22</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -3635,10 +4166,10 @@
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="H6" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -3649,10 +4180,10 @@
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="J7" s="1">
         <v>100</v>
@@ -3663,10 +4194,10 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J8" s="1">
         <v>101</v>
@@ -3677,10 +4208,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
       <c r="H9" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="J9" s="1">
         <v>102</v>
@@ -3691,13 +4222,24 @@
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="H10" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J10" s="1">
         <v>103</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:12">
+      <c r="H11" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="J11" s="1">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
